--- a/hourly datasets/cap_gen_year1final.xlsx
+++ b/hourly datasets/cap_gen_year1final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09997464971745799</v>
+        <v>0.09921008450332293</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0870436897600398</v>
+        <v>0.08311574323195325</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1870183394774978</v>
+        <v>0.1823258277352762</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1404651350714983</v>
+        <v>0.14137084786437</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2404397847889563</v>
+        <v>0.2405809323676929</v>
       </c>
     </row>
     <row r="5">
@@ -531,15 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04737453848398046</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+        <v>0.0396014990282015</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.005477459680095793</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.983960142246695</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.03718073906221341</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02884224267162464</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05036075538477861</v>
+      </c>
       <c r="H5" t="n">
-        <v>0.1473491882014384</v>
+        <v>0.1388115835315244</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +559,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04164534289154693</v>
+        <v>0.03327897343547968</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00758821968299475</v>
+        <v>0.005869263635955893</v>
       </c>
       <c r="D6" t="n">
-        <v>3.234991697728881</v>
+        <v>2.951425752691496</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04027346932383607</v>
+        <v>0.02957225627486669</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02664642311026557</v>
+        <v>0.02171346020265332</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05664426267282812</v>
+        <v>0.0448444866683063</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1416199926090049</v>
+        <v>0.1324890579388026</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +587,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02766585445522624</v>
+        <v>0.02087195947713457</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00779535697115388</v>
+        <v>0.006097303548148693</v>
       </c>
       <c r="D7" t="n">
-        <v>1.887231479864464</v>
+        <v>1.670996680159912</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04059096086069674</v>
+        <v>0.02624415634600928</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01231001800819922</v>
+        <v>0.008889802916033345</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04302169090225323</v>
+        <v>0.03285411603823601</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1276405041726842</v>
+        <v>0.1200820439804575</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +615,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02470149967721591</v>
+        <v>0.01638904806089585</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004684855644768912</v>
+        <v>0.001933389857261307</v>
       </c>
       <c r="D8" t="n">
-        <v>1.389282604641385</v>
+        <v>1.104602172308657</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01315195166956533</v>
+        <v>0.002668555100280951</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01544761526769005</v>
+        <v>0.01259706188511474</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03395538408674198</v>
+        <v>0.02018103423667707</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1246761493946739</v>
+        <v>0.1155991325642188</v>
       </c>
     </row>
     <row r="9">
@@ -633,15 +643,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01888326388650609</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+        <v>0.00903532240009757</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.001197609615071388</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6789290741208116</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.006437431133230117</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.006678333166215253</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01139231163397993</v>
+      </c>
       <c r="H9" t="n">
-        <v>0.1188579136039641</v>
+        <v>0.1082454069034205</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +671,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02369878698745892</v>
+        <v>0.01218575689158484</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004273605237485141</v>
+        <v>0.001975555758038307</v>
       </c>
       <c r="D10" t="n">
-        <v>1.042120459021991</v>
+        <v>0.5470168772383992</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01100731430426948</v>
+        <v>0.002218351265123574</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01519526873048314</v>
+        <v>0.008250431391028176</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03220230524443489</v>
+        <v>0.01612108239214163</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1236734367049169</v>
+        <v>0.1113958413949078</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +699,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02400530286068364</v>
+        <v>0.0236356935421389</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +707,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1239799525781416</v>
+        <v>0.1228457780454618</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +717,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03883669499125091</v>
+        <v>0.03828813152179772</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +725,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1388113447087089</v>
+        <v>0.1374982160251206</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +735,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04944992167375207</v>
+        <v>0.04838920301403452</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +743,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1494245713912101</v>
+        <v>0.1475992875173575</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05444133214279879</v>
+        <v>0.05427180685755705</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +761,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1544159818602568</v>
+        <v>0.15348189136088</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +771,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06059297091547133</v>
+        <v>0.05850903528330267</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +779,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1605676206329293</v>
+        <v>0.1577191197866256</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +789,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06293349958891602</v>
+        <v>0.06137382385333409</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +797,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.162908149306374</v>
+        <v>0.160583908356657</v>
       </c>
     </row>
     <row r="17">
@@ -787,25 +807,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06673435934246637</v>
+        <v>0.06522548254207212</v>
       </c>
       <c r="C17" t="n">
-        <v>0.009175963386418757</v>
+        <v>0.008818294608826894</v>
       </c>
       <c r="D17" t="n">
-        <v>11.51049643918773</v>
+        <v>11.73033860090766</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05719195765868181</v>
+        <v>0.05712521043453614</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04864231096523789</v>
+        <v>0.04784193304588754</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08482640771969492</v>
+        <v>0.08260903203825677</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1667090090599244</v>
+        <v>0.1644355670453951</v>
       </c>
     </row>
     <row r="18">
@@ -815,22 +835,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09997464971745799</v>
+        <v>-0.09921008450332293</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01295305454255576</v>
+        <v>0.01230608521789927</v>
       </c>
       <c r="D18" t="n">
-        <v>-14.80351988215079</v>
+        <v>-15.20724502395064</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05011510350319052</v>
+        <v>0.05005365880838259</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1255028878472522</v>
+        <v>-0.1234345835047094</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07444641158766359</v>
+        <v>-0.07498558550193614</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -843,25 +863,15 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06843837116250542</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.009476054681405473</v>
-      </c>
-      <c r="D19" t="n">
-        <v>12.02898695325092</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.05792681307000966</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.04973236581928257</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.08714437650572826</v>
-      </c>
+        <v>0.0676128609138522</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1684130208799634</v>
+        <v>0.1668229454171751</v>
       </c>
     </row>
     <row r="20">
@@ -871,7 +881,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0730291089370923</v>
+        <v>0.07015543429754201</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -879,7 +889,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1730037586545503</v>
+        <v>0.1693655188008649</v>
       </c>
     </row>
     <row r="21">
@@ -889,25 +899,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.07102478244049937</v>
+        <v>0.06961174876515283</v>
       </c>
       <c r="C21" t="n">
-        <v>0.009455517814283712</v>
+        <v>0.009328390375462564</v>
       </c>
       <c r="D21" t="n">
-        <v>12.07657423541167</v>
+        <v>12.31077289661105</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05720708924962065</v>
+        <v>0.05702010169662995</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05237497107718301</v>
+        <v>0.05121830830513232</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08967459380381548</v>
+        <v>0.08800518922517322</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1709994321579574</v>
+        <v>0.1688218332684758</v>
       </c>
     </row>
     <row r="22">
@@ -917,25 +927,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07417030871005445</v>
+        <v>0.07106768035075121</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009456611837933062</v>
+        <v>0.009210874765701328</v>
       </c>
       <c r="D22" t="n">
-        <v>12.23124135819625</v>
+        <v>12.37050170540738</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05186039735443365</v>
+        <v>0.05407649103722381</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05557909314717292</v>
+        <v>0.05295861516437383</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09276152427293605</v>
+        <v>0.08917674553712859</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1741449584275124</v>
+        <v>0.1702777648540741</v>
       </c>
     </row>
     <row r="23">
@@ -945,25 +955,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.07723988582087125</v>
+        <v>0.07459519650955213</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009865516281999449</v>
+        <v>0.009478454161735379</v>
       </c>
       <c r="D23" t="n">
-        <v>12.48328589402987</v>
+        <v>12.67148831417835</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06059043561897473</v>
+        <v>0.06199190358787368</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05778157783675395</v>
+        <v>0.05591001647353776</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09669819380498867</v>
+        <v>0.09328037654556681</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1772145355383292</v>
+        <v>0.1738052810128751</v>
       </c>
     </row>
     <row r="24">
@@ -973,25 +983,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.07718602813600076</v>
+        <v>0.07465921083914781</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009728480677344241</v>
+        <v>0.009362167227001009</v>
       </c>
       <c r="D24" t="n">
-        <v>12.6064153140849</v>
+        <v>12.71165877101719</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06213822187789601</v>
+        <v>0.06276285791257985</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05801727871975782</v>
+        <v>0.05622197718813733</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09635477755224384</v>
+        <v>0.09309644449015823</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1771606778534587</v>
+        <v>0.1738692953424708</v>
       </c>
     </row>
     <row r="25">
@@ -1001,7 +1011,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.07734879572187313</v>
+        <v>0.07421731214711626</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1009,7 +1019,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.1773234454393311</v>
+        <v>0.1734273966504392</v>
       </c>
     </row>
     <row r="26">
@@ -1019,25 +1029,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.07825374208207501</v>
+        <v>0.07706702421642694</v>
       </c>
       <c r="C26" t="n">
-        <v>0.009748176530615457</v>
+        <v>0.009418365982273304</v>
       </c>
       <c r="D26" t="n">
-        <v>12.50851141378558</v>
+        <v>12.72635293979622</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05652768866642089</v>
+        <v>0.05846950433656978</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05901889424862341</v>
+        <v>0.0584968742608403</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09748858991552674</v>
+        <v>0.09563717417201363</v>
       </c>
       <c r="H26" t="n">
-        <v>0.178228391799533</v>
+        <v>0.1762771087197499</v>
       </c>
     </row>
     <row r="27">
@@ -1047,25 +1057,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07918421373277997</v>
+        <v>0.07656162734876724</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009274613235989191</v>
+        <v>0.009020748958978338</v>
       </c>
       <c r="D27" t="n">
-        <v>12.61071850318415</v>
+        <v>12.84104926742213</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06203709638046995</v>
+        <v>0.06141290885957201</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06094615922916893</v>
+        <v>0.05882651665916971</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09742226823639089</v>
+        <v>0.09429673803836447</v>
       </c>
       <c r="H27" t="n">
-        <v>0.179158863450238</v>
+        <v>0.1757717118520902</v>
       </c>
     </row>
     <row r="28">
@@ -1075,25 +1085,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08391664963040281</v>
+        <v>0.08112602767032216</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01020587934181395</v>
+        <v>0.009721182762680044</v>
       </c>
       <c r="D28" t="n">
-        <v>12.5630685237041</v>
+        <v>12.91839655757368</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09219881588401212</v>
+        <v>0.08631430380354026</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06382598427914278</v>
+        <v>0.06201578475728806</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1040073149816627</v>
+        <v>0.1002362705833567</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1838912993478608</v>
+        <v>0.1803361121736451</v>
       </c>
     </row>
     <row r="29">
@@ -1103,25 +1113,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02579560098016311</v>
+        <v>0.02471889494798388</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01163375223296176</v>
+        <v>0.005040946070318424</v>
       </c>
       <c r="D29" t="n">
-        <v>3.930030570390517</v>
+        <v>1.855849536215534</v>
       </c>
       <c r="E29" t="n">
-        <v>0.008226197361249696</v>
+        <v>0.006474177808161229</v>
       </c>
       <c r="F29" t="n">
-        <v>0.002764995551323798</v>
+        <v>0.0147476684966657</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04882620640900252</v>
+        <v>0.03469012139930158</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1257702506976211</v>
+        <v>0.1239289794513068</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year1final.xlsx
+++ b/hourly datasets/cap_gen_year1final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2209544015212427</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09921008450332293</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09454686769455165</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08311574323195325</v>
+        <v>0.3215387308603738</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1823258277352762</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1951311970336827</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.14137084786437</v>
+        <v>0.3304035086668322</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2405809323676929</v>
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2039959748401412</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0396014990282015</v>
+        <v>0.3401263982261845</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005477459680095793</v>
+        <v>0.007237861425461699</v>
       </c>
       <c r="D5" t="n">
-        <v>5.983960142246695</v>
+        <v>4.83787257852519</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03718073906221341</v>
+        <v>0.04076109257463088</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02884224267162464</v>
+        <v>0.02369031602888765</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05036075538477861</v>
+        <v>0.05212842050807536</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1388115835315244</v>
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2137188643994935</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +576,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03327897343547968</v>
+        <v>0.3565062700277295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005869263635955893</v>
+        <v>0.00861990476412317</v>
       </c>
       <c r="D6" t="n">
-        <v>2.951425752691496</v>
+        <v>4.618757373278234</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02957225627486669</v>
+        <v>0.04139450507803651</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02171346020265332</v>
+        <v>0.0239813869993706</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0448444866683063</v>
+        <v>0.05793454384173712</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1324890579388026</v>
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2300987362010385</v>
       </c>
     </row>
     <row r="7">
@@ -587,25 +607,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02087195947713457</v>
+        <v>0.3061657756877924</v>
       </c>
       <c r="C7" t="n">
-        <v>0.006097303548148693</v>
+        <v>0.09640332618112546</v>
       </c>
       <c r="D7" t="n">
-        <v>1.670996680159912</v>
+        <v>4.250578611844491</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02624415634600928</v>
+        <v>0.4365501897992944</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008889802916033345</v>
+        <v>-0.09574218692854035</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03285411603823601</v>
+        <v>0.2824019982705772</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1200820439804575</v>
+        <v>65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1797582418611013</v>
       </c>
     </row>
     <row r="8">
@@ -615,25 +638,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01638904806089585</v>
+        <v>0.1826962916573034</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001933389857261307</v>
+        <v>0.01759929080716825</v>
       </c>
       <c r="D8" t="n">
-        <v>1.104602172308657</v>
+        <v>8.630176176873185</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002668555100280951</v>
+        <v>0.002958608769467668</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01259706188511474</v>
+        <v>0.1130570496011856</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02018103423667707</v>
+        <v>0.1820615821512334</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1155991325642188</v>
+        <v>67</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05628875783061241</v>
       </c>
     </row>
     <row r="9">
@@ -643,25 +669,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00903532240009757</v>
+        <v>0.1630507327210351</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001197609615071388</v>
+        <v>0.01669169388134573</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6789290741208116</v>
+        <v>8.380903429810074</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006437431133230117</v>
+        <v>0.008406499550228498</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006678333166215253</v>
+        <v>0.1050257338993534</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01139231163397993</v>
+        <v>0.170487620202736</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1082454069034205</v>
+        <v>67</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.03664319889434409</v>
       </c>
     </row>
     <row r="10">
@@ -671,25 +700,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01218575689158484</v>
+        <v>0.1684554389103767</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001975555758038307</v>
+        <v>0.0191917163491807</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5470168772383992</v>
+        <v>7.893514597569126</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002218351265123574</v>
+        <v>0.002532786454697782</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008250431391028176</v>
+        <v>0.1057455511091139</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01612108239214163</v>
+        <v>0.1813927907920453</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1113958413949078</v>
+        <v>67</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.04204790508368567</v>
       </c>
     </row>
     <row r="11">
@@ -699,7 +731,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0236356935421389</v>
+        <v>0.2554684732603537</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -707,7 +739,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1228457780454618</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1290609394336627</v>
       </c>
     </row>
     <row r="12">
@@ -717,7 +752,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03828813152179772</v>
+        <v>0.27425982785479</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -725,7 +760,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1374982160251206</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1478522940280989</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +773,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04838920301403452</v>
+        <v>0.2864819428859363</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -743,7 +781,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1475992875173575</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1600744090592453</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +794,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05427180685755705</v>
+        <v>0.2942525403770541</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -761,7 +802,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.15348189136088</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1678450065503631</v>
       </c>
     </row>
     <row r="15">
@@ -771,7 +815,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05850903528330267</v>
+        <v>0.3009514783201842</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -779,7 +823,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1577191197866256</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1745439444934931</v>
       </c>
     </row>
     <row r="16">
@@ -789,7 +836,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06137382385333409</v>
+        <v>0.3050611153732678</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -797,7 +844,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.160583908356657</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1786535815465768</v>
       </c>
     </row>
     <row r="17">
@@ -807,25 +857,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06522548254207212</v>
+        <v>0.3101056688209922</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008818294608826894</v>
+        <v>0.008808958628211506</v>
       </c>
       <c r="D17" t="n">
-        <v>11.73033860090766</v>
+        <v>11.72035605973623</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05712521043453614</v>
+        <v>0.05702045452629617</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04784193304588754</v>
+        <v>0.04778277574723078</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08260903203825677</v>
+        <v>0.08251291424443925</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1644355670453951</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1836981349943011</v>
       </c>
     </row>
     <row r="18">
@@ -835,24 +888,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09921008450332293</v>
+        <v>0.126407533826691</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01230608521789927</v>
+        <v>0.01209343368132089</v>
       </c>
       <c r="D18" t="n">
-        <v>-15.20724502395064</v>
+        <v>-15.08954297422754</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05005365880838259</v>
+        <v>0.04934266818715839</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1234345835047094</v>
+        <v>-0.1217418891492827</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07498558550193614</v>
+        <v>-0.07412788982603452</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -863,7 +919,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0676128609138522</v>
+        <v>0.3135105172264735</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -871,7 +927,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1668229454171751</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1871029833997825</v>
       </c>
     </row>
     <row r="20">
@@ -881,7 +940,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.07015543429754201</v>
+        <v>0.3140426095304555</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -889,7 +948,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1693655188008649</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1876350757037644</v>
       </c>
     </row>
     <row r="21">
@@ -899,25 +961,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.06961174876515283</v>
+        <v>0.3143031640322296</v>
       </c>
       <c r="C21" t="n">
-        <v>0.009328390375462564</v>
+        <v>0.009292799131148973</v>
       </c>
       <c r="D21" t="n">
-        <v>12.31077289661105</v>
+        <v>12.27931166275598</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05702010169662995</v>
+        <v>0.05693885447534943</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05121830830513232</v>
+        <v>0.05095090866228802</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08800518922517322</v>
+        <v>0.08759781701776967</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1688218332684758</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1878956302055385</v>
       </c>
     </row>
     <row r="22">
@@ -927,25 +992,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07106768035075121</v>
+        <v>0.3174758512033686</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009210874765701328</v>
+        <v>0.009157457675745535</v>
       </c>
       <c r="D22" t="n">
-        <v>12.37050170540738</v>
+        <v>12.32651408551471</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05407649103722381</v>
+        <v>0.05398036526102871</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05295861516437383</v>
+        <v>0.05257116974374208</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08917674553712859</v>
+        <v>0.08857952917027179</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1702777648540741</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1910683173766775</v>
       </c>
     </row>
     <row r="23">
@@ -955,25 +1023,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.07459519650955213</v>
+        <v>0.3203194304169851</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009478454161735379</v>
+        <v>0.009416619233481683</v>
       </c>
       <c r="D23" t="n">
-        <v>12.67148831417835</v>
+        <v>12.6159093535755</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06199190358787368</v>
+        <v>0.0617184614941816</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05591001647353776</v>
+        <v>0.05541547912496925</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09328037654556681</v>
+        <v>0.09254310081448029</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1738052810128751</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1939118965902941</v>
       </c>
     </row>
     <row r="24">
@@ -983,25 +1054,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.07465921083914781</v>
+        <v>0.3201354136071061</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009362167227001009</v>
+        <v>0.009314510604779324</v>
       </c>
       <c r="D24" t="n">
-        <v>12.71165877101719</v>
+        <v>12.66084046076192</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06276285791257985</v>
+        <v>0.06259312800036741</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05622197718813733</v>
+        <v>0.05575796913314993</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09309644449015823</v>
+        <v>0.09244500489485215</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1738692953424708</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1937278797804151</v>
       </c>
     </row>
     <row r="25">
@@ -1011,7 +1085,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.07421731214711626</v>
+        <v>0.32190359540139</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1019,7 +1093,10 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.1734273966504392</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1954960615746989</v>
       </c>
     </row>
     <row r="26">
@@ -1029,25 +1106,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.07706702421642694</v>
+        <v>0.3212963053856583</v>
       </c>
       <c r="C26" t="n">
-        <v>0.009418365982273304</v>
+        <v>0.009341797547376671</v>
       </c>
       <c r="D26" t="n">
-        <v>12.72635293979622</v>
+        <v>12.57207792971844</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05846950433656978</v>
+        <v>0.05838037753571358</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0584968742608403</v>
+        <v>0.05734160858204646</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09563717417201363</v>
+        <v>0.094181017703573</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1762771087197499</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1948887715589672</v>
       </c>
     </row>
     <row r="27">
@@ -1057,25 +1137,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07656162734876724</v>
+        <v>0.3238985156893979</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009020748958978338</v>
+        <v>0.008937881885842514</v>
       </c>
       <c r="D27" t="n">
-        <v>12.84104926742213</v>
+        <v>12.73437444181639</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06141290885957201</v>
+        <v>0.05998528702930291</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05882651665916971</v>
+        <v>0.0581679745896808</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09429673803836447</v>
+        <v>0.09331201682075795</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1757717118520902</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1974909818627069</v>
       </c>
     </row>
     <row r="28">
@@ -1085,25 +1168,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08112602767032216</v>
+        <v>0.3202751392381932</v>
       </c>
       <c r="C28" t="n">
-        <v>0.009721182762680044</v>
+        <v>0.009519005764764424</v>
       </c>
       <c r="D28" t="n">
-        <v>12.91839655757368</v>
+        <v>12.64360348324294</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08631430380354026</v>
+        <v>0.08142400119950928</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06201578475728806</v>
+        <v>0.06010640020240544</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1002362705833567</v>
+        <v>0.09753119329541485</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1803361121736451</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1938676054115021</v>
       </c>
     </row>
     <row r="29">
@@ -1113,25 +1199,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02471889494798388</v>
+        <v>0.3802835122428506</v>
       </c>
       <c r="C29" t="n">
-        <v>0.005040946070318424</v>
+        <v>0.07545792967478336</v>
       </c>
       <c r="D29" t="n">
-        <v>1.855849536215534</v>
+        <v>6.880878363954064</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006474177808161229</v>
+        <v>0.1044490252879627</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0147476684966657</v>
+        <v>0.02583162664022561</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03469012139930158</v>
+        <v>0.322267604628693</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1239289794513068</v>
+        <v>65</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2538759784161596</v>
       </c>
     </row>
   </sheetData>
